--- a/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
+++ b/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>The data is profiled before it is touched, every cleaning call is in the decisions log with its reason, and counts and rupees reconcile across files.</t>
+          <t>The data is profiled before it is touched, every cleaning call is in the decisions log with its reason, and counts and dollars reconcile across files.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">

--- a/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
+++ b/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,12 @@
       <b val="1"/>
       <color rgb="001A0F5C"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A0F5C"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -96,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4B8"/>
+        <fgColor rgb="00FFF4C2"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,28 +132,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -513,61 +518,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Build 1 mini project scoring sheet (TRAINER ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+          <t>How is each Build 1 group and each learner scored on the mini project? (TRAINER ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>The rubric is Build 1's mini project rubric as the requester approved it on 29 September 2026, recorded in data/programme/facts.yaml (evaluation.rubrics.W03). The first four criteria are scored once for the group, and every member receives those 34 marks; presentation and defence is scored for each learner on 6 marks, so a silent teammate cannot ride the group's score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>The rubric</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Build 1's mini project rubric as the requester approved it on 29 September 2026, copied from data/programme/facts.yaml (evaluation.rubrics.W03) onto the Rubric sheet. The first four criteria are scored once for the group, and every member receives those 34 marks; presentation and defence is scored for each learner on 6 marks, so a silent teammate cannot ride the group's score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yellow cells with blue text are the inputs. On Groups: the sub-problem, the panel, the day, and the four group criteria. On Learners: whether the seat is in use and the presentation and defence score. Totals, checks and the summary are formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Where to type</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Only the yellow cells. On Groups: the sub-problem, the panel, the day, the demo's outcome and the four group criteria. On Learners: whether the seat is in use and the presentation and defence score. Every other cell is a formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Score each group after its slot, never in front of it, from the panel's evidence notes and the question bank (content/W03/SAT/trainer/C2_W03_SAT_question_bank_TRAINER.md). A silent teammate's presentation and defence score waits for the separate question in the room's reserve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>When to score</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>After the slot, never in front of the group, from the panel's evidence notes and the question bank (trainer/C2_W03_SAT_question_bank_TRAINER.md). A quiet member's presentation and defence score waits for the separate questions in the room's reserve; the group's 34 does not wait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>The demo rule on both expert days: a group's demo runs once, cold, on its raw files. If it fails, the group has two minutes to recover it live, as it would in front of a client. If it still fails, the group presents from its executed notebook, and the panel scores the live demo in presentation and defence as not run cold. The other 34 marks of the mini project are scored from the executed run, so a failed demo costs its own marks and never the analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>The demo rule</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A group's demo runs once, cold, on its raw files. If it fails, the group has two minutes to recover it live, as it would in front of a client. If it still fails, the group presents from its executed notebook, and the panel scores the live demo in presentation and defence as not run cold. The other 34 marks of the mini project are scored from the executed run, so a failed demo costs its own marks and never the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>The Learners sheet holds 35 seats, one per learner: eight groups of four and G9 of three. Relabel the seats if Monday's allocation put the group of three elsewhere. Mark an absent learner N in the In use column; the row then reads absent and drops out of the counts. An absence is recorded with the Programme Head's decision in the grade closure workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>How the sheet applies it</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Record each group's demo outcome on Groups. The group part is scored from the executed run whatever the outcome, so it is never left blank because a demo failed. A learner in a group whose demo still failed cannot carry full marks on presentation and defence, since the rubric's full marks there begin with a demo that runs cold; the Learners check flags it, and how far below full is the panel's call. A demo held up by a failed machine runs cold in the room's reserve before anyone's presentation and defence is scored, and its outcome replaces the machine entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Each learner's total out of 40 is copied once into the grade closure workbook (C2_W03_SAT_grade_closure_TRAINER.xlsx, Scores, Mini project). Learner names go only into the copy the Programme Head keeps, never into the committed file, because the repository is public.</t>
+          <t>Seats, never names</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>35 seats, one per learner: eight groups of four and G9 of three. Relabel the seats if Monday's allocation put the group of three elsewhere. Mark an absent learner N in In use; the row then reads absent and drops out of the counts. The Programme Head records the absence and the decision in the grade closure workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Where the scores go</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Each learner's group part (of 34) and presentation and defence (of 6) are copied once into the grade closure workbook (C2_W03_SAT_grade_closure_TRAINER.xlsx, sheet Scores), and each group's demo outcome into its Demos sheet. Names go only into the copy the Programme Head keeps, never into the committed file, because the repository is public.</t>
         </is>
       </c>
     </row>
@@ -592,158 +637,158 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Mini project rubric, 40 marks per learner</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mini project rubric: 40 marks per learner</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>What full marks look like</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Scored</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>The question translated</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Dr Menon's words are mapped to the right Weeks 1 and 2 method, with the metric defined and the decision it feeds named.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>once per group</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>The data made trustworthy</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>The data is profiled before it is touched, every cleaning call is in the decisions log with its reason, and counts and dollars reconcile across files.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>once per group</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>The analysis</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>The tree, ladder or fair comparison reaches the branch that explains the symptom, on the right denominator, with a chance test where one is needed.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>once per group</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>The claim</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>One sentence carries its number, denominator, period and caveat, plus an action Dr Menon can take.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>once per group</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Presentation and defence</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>The live demo runs cold, and every member answers a challenge on the caveat.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>per learner</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <f>SUM(B3:B7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Group part</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f>SUM(B3:B6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Source: data/programme/facts.yaml, evaluation.rubrics.W03.events.mini-project, approved 29 September 2026.</t>
         </is>
@@ -760,280 +805,337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Groups: the four group criteria, scored once per group</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Groups: the demo's outcome and the four group criteria, scored once per group</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Sub-problem</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Panel</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Demo on the day</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>The question translated (of 8)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>The data made trustworthy (of 10)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>The analysis (of 10)</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>The claim (of 6)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Group part (of 34)</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>What the demo rule means for this group</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="8">
-        <f>IF(COUNT(E3:H3)&lt;4,"incomplete",SUM(E3:H3))</f>
-        <v/>
-      </c>
-      <c r="J3" s="8">
-        <f>IF(OR(E3&gt;Rubric!$B$3,F3&gt;Rubric!$B$4,G3&gt;Rubric!$B$5,H3&gt;Rubric!$B$6,MIN(E3:H3)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="9">
+        <f>IF(COUNT(F3:I3)&lt;4,"incomplete",SUM(F3:I3))</f>
+        <v/>
+      </c>
+      <c r="K3" s="9">
+        <f>IF(OR(F3&gt;Rubric!$B$3,G3&gt;Rubric!$B$4,H3&gt;Rubric!$B$5,I3&gt;Rubric!$B$6,MIN(F3:I3)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F3:I3)&gt;0,E3=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L3" s="6">
+        <f>IF(E3="","record the demo's outcome",IF(E3="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E3="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="8">
-        <f>IF(COUNT(E4:H4)&lt;4,"incomplete",SUM(E4:H4))</f>
-        <v/>
-      </c>
-      <c r="J4" s="8">
-        <f>IF(OR(E4&gt;Rubric!$B$3,F4&gt;Rubric!$B$4,G4&gt;Rubric!$B$5,H4&gt;Rubric!$B$6,MIN(E4:H4)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="9">
+        <f>IF(COUNT(F4:I4)&lt;4,"incomplete",SUM(F4:I4))</f>
+        <v/>
+      </c>
+      <c r="K4" s="9">
+        <f>IF(OR(F4&gt;Rubric!$B$3,G4&gt;Rubric!$B$4,H4&gt;Rubric!$B$5,I4&gt;Rubric!$B$6,MIN(F4:I4)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F4:I4)&gt;0,E4=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>IF(E4="","record the demo's outcome",IF(E4="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E4="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="8">
-        <f>IF(COUNT(E5:H5)&lt;4,"incomplete",SUM(E5:H5))</f>
-        <v/>
-      </c>
-      <c r="J5" s="8">
-        <f>IF(OR(E5&gt;Rubric!$B$3,F5&gt;Rubric!$B$4,G5&gt;Rubric!$B$5,H5&gt;Rubric!$B$6,MIN(E5:H5)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="9">
+        <f>IF(COUNT(F5:I5)&lt;4,"incomplete",SUM(F5:I5))</f>
+        <v/>
+      </c>
+      <c r="K5" s="9">
+        <f>IF(OR(F5&gt;Rubric!$B$3,G5&gt;Rubric!$B$4,H5&gt;Rubric!$B$5,I5&gt;Rubric!$B$6,MIN(F5:I5)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F5:I5)&gt;0,E5=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="6">
+        <f>IF(E5="","record the demo's outcome",IF(E5="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E5="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="8">
-        <f>IF(COUNT(E6:H6)&lt;4,"incomplete",SUM(E6:H6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="8">
-        <f>IF(OR(E6&gt;Rubric!$B$3,F6&gt;Rubric!$B$4,G6&gt;Rubric!$B$5,H6&gt;Rubric!$B$6,MIN(E6:H6)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="9">
+        <f>IF(COUNT(F6:I6)&lt;4,"incomplete",SUM(F6:I6))</f>
+        <v/>
+      </c>
+      <c r="K6" s="9">
+        <f>IF(OR(F6&gt;Rubric!$B$3,G6&gt;Rubric!$B$4,H6&gt;Rubric!$B$5,I6&gt;Rubric!$B$6,MIN(F6:I6)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F6:I6)&gt;0,E6=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>IF(E6="","record the demo's outcome",IF(E6="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E6="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="8">
-        <f>IF(COUNT(E7:H7)&lt;4,"incomplete",SUM(E7:H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="8">
-        <f>IF(OR(E7&gt;Rubric!$B$3,F7&gt;Rubric!$B$4,G7&gt;Rubric!$B$5,H7&gt;Rubric!$B$6,MIN(E7:H7)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="9">
+        <f>IF(COUNT(F7:I7)&lt;4,"incomplete",SUM(F7:I7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="9">
+        <f>IF(OR(F7&gt;Rubric!$B$3,G7&gt;Rubric!$B$4,H7&gt;Rubric!$B$5,I7&gt;Rubric!$B$6,MIN(F7:I7)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F7:I7)&gt;0,E7=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>IF(E7="","record the demo's outcome",IF(E7="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E7="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="8">
-        <f>IF(COUNT(E8:H8)&lt;4,"incomplete",SUM(E8:H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="8">
-        <f>IF(OR(E8&gt;Rubric!$B$3,F8&gt;Rubric!$B$4,G8&gt;Rubric!$B$5,H8&gt;Rubric!$B$6,MIN(E8:H8)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="9">
+        <f>IF(COUNT(F8:I8)&lt;4,"incomplete",SUM(F8:I8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="9">
+        <f>IF(OR(F8&gt;Rubric!$B$3,G8&gt;Rubric!$B$4,H8&gt;Rubric!$B$5,I8&gt;Rubric!$B$6,MIN(F8:I8)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F8:I8)&gt;0,E8=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>IF(E8="","record the demo's outcome",IF(E8="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E8="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="8">
-        <f>IF(COUNT(E9:H9)&lt;4,"incomplete",SUM(E9:H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="8">
-        <f>IF(OR(E9&gt;Rubric!$B$3,F9&gt;Rubric!$B$4,G9&gt;Rubric!$B$5,H9&gt;Rubric!$B$6,MIN(E9:H9)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="9">
+        <f>IF(COUNT(F9:I9)&lt;4,"incomplete",SUM(F9:I9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="9">
+        <f>IF(OR(F9&gt;Rubric!$B$3,G9&gt;Rubric!$B$4,H9&gt;Rubric!$B$5,I9&gt;Rubric!$B$6,MIN(F9:I9)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F9:I9)&gt;0,E9=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IF(E9="","record the demo's outcome",IF(E9="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E9="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="8">
-        <f>IF(COUNT(E10:H10)&lt;4,"incomplete",SUM(E10:H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="8">
-        <f>IF(OR(E10&gt;Rubric!$B$3,F10&gt;Rubric!$B$4,G10&gt;Rubric!$B$5,H10&gt;Rubric!$B$6,MIN(E10:H10)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="9">
+        <f>IF(COUNT(F10:I10)&lt;4,"incomplete",SUM(F10:I10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="9">
+        <f>IF(OR(F10&gt;Rubric!$B$3,G10&gt;Rubric!$B$4,H10&gt;Rubric!$B$5,I10&gt;Rubric!$B$6,MIN(F10:I10)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F10:I10)&gt;0,E10=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f>IF(E10="","record the demo's outcome",IF(E10="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E10="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="8">
-        <f>IF(COUNT(E11:H11)&lt;4,"incomplete",SUM(E11:H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="8">
-        <f>IF(OR(E11&gt;Rubric!$B$3,F11&gt;Rubric!$B$4,G11&gt;Rubric!$B$5,H11&gt;Rubric!$B$6,MIN(E11:H11)&lt;0),"above a maximum or below zero","ok")</f>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="9">
+        <f>IF(COUNT(F11:I11)&lt;4,"incomplete",SUM(F11:I11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="9">
+        <f>IF(OR(F11&gt;Rubric!$B$3,G11&gt;Rubric!$B$4,H11&gt;Rubric!$B$5,I11&gt;Rubric!$B$6,MIN(F11:I11)&lt;0),"above a maximum or below zero",IF(AND(COUNT(F11:I11)&gt;0,E11=""),"record the demo's outcome","ok"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>IF(E11="","record the demo's outcome",IF(E11="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E11="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B3 B4 B5 B6 B7 B8 B9 B10 B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1 revenue,2 bookings,3 billing,4 no-shows,5 campaign"</formula1>
     </dataValidation>
@@ -1042,6 +1144,9 @@
     </dataValidation>
     <dataValidation sqref="D3 D4 D5 D6 D7 D8 D9 D10 D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Friday,Saturday"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3 E4 E5 E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ran cold,recovered within two minutes,still failed: presented from the executed notebook,machine failed: demo waits for the reserve"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1054,1039 +1159,1185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Learners: presentation and defence per learner, and each learner's total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Seat</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>In use (Y or N)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Presentation and defence (of 6)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Demo on the day</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Group part (of 34)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Total (of 40)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A3,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F3" s="8">
-        <f>IF(C3="N","absent",IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(E3))),"incomplete",D3+E3))</f>
-        <v/>
-      </c>
-      <c r="G3" s="8">
-        <f>IF(AND(ISNUMBER(D3),OR(D3&gt;Rubric!$B$7,D3&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A3,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A3,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F3" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A3,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G3" s="9">
+        <f>IF(C3="N","absent",IF(OR(NOT(ISNUMBER(D3)),NOT(ISNUMBER(F3))),"incomplete",D3+F3))</f>
+        <v/>
+      </c>
+      <c r="H3" s="9">
+        <f>IF(AND(ISNUMBER(D3),OR(D3&gt;Rubric!$B$7,D3&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D3),E3="still failed: presented from the executed notebook",D3&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D3),E3="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A4,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F4" s="8">
-        <f>IF(C4="N","absent",IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(E4))),"incomplete",D4+E4))</f>
-        <v/>
-      </c>
-      <c r="G4" s="8">
-        <f>IF(AND(ISNUMBER(D4),OR(D4&gt;Rubric!$B$7,D4&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A4,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A4,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F4" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A4,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G4" s="9">
+        <f>IF(C4="N","absent",IF(OR(NOT(ISNUMBER(D4)),NOT(ISNUMBER(F4))),"incomplete",D4+F4))</f>
+        <v/>
+      </c>
+      <c r="H4" s="9">
+        <f>IF(AND(ISNUMBER(D4),OR(D4&gt;Rubric!$B$7,D4&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D4),E4="still failed: presented from the executed notebook",D4&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D4),E4="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A5,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F5" s="8">
-        <f>IF(C5="N","absent",IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(E5))),"incomplete",D5+E5))</f>
-        <v/>
-      </c>
-      <c r="G5" s="8">
-        <f>IF(AND(ISNUMBER(D5),OR(D5&gt;Rubric!$B$7,D5&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A5,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A5,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F5" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A5,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G5" s="9">
+        <f>IF(C5="N","absent",IF(OR(NOT(ISNUMBER(D5)),NOT(ISNUMBER(F5))),"incomplete",D5+F5))</f>
+        <v/>
+      </c>
+      <c r="H5" s="9">
+        <f>IF(AND(ISNUMBER(D5),OR(D5&gt;Rubric!$B$7,D5&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D5),E5="still failed: presented from the executed notebook",D5&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D5),E5="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A6,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="8">
-        <f>IF(C6="N","absent",IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(E6))),"incomplete",D6+E6))</f>
-        <v/>
-      </c>
-      <c r="G6" s="8">
-        <f>IF(AND(ISNUMBER(D6),OR(D6&gt;Rubric!$B$7,D6&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A6,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A6,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A6,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>IF(C6="N","absent",IF(OR(NOT(ISNUMBER(D6)),NOT(ISNUMBER(F6))),"incomplete",D6+F6))</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>IF(AND(ISNUMBER(D6),OR(D6&gt;Rubric!$B$7,D6&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D6),E6="still failed: presented from the executed notebook",D6&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D6),E6="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A7,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F7" s="8">
-        <f>IF(C7="N","absent",IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(E7))),"incomplete",D7+E7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="8">
-        <f>IF(AND(ISNUMBER(D7),OR(D7&gt;Rubric!$B$7,D7&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A7,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A7,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A7,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(C7="N","absent",IF(OR(NOT(ISNUMBER(D7)),NOT(ISNUMBER(F7))),"incomplete",D7+F7))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(AND(ISNUMBER(D7),OR(D7&gt;Rubric!$B$7,D7&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D7),E7="still failed: presented from the executed notebook",D7&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D7),E7="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A8,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F8" s="8">
-        <f>IF(C8="N","absent",IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(E8))),"incomplete",D8+E8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="8">
-        <f>IF(AND(ISNUMBER(D8),OR(D8&gt;Rubric!$B$7,D8&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A8,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A8,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F8" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A8,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>IF(C8="N","absent",IF(OR(NOT(ISNUMBER(D8)),NOT(ISNUMBER(F8))),"incomplete",D8+F8))</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>IF(AND(ISNUMBER(D8),OR(D8&gt;Rubric!$B$7,D8&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D8),E8="still failed: presented from the executed notebook",D8&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D8),E8="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A9,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F9" s="8">
-        <f>IF(C9="N","absent",IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(E9))),"incomplete",D9+E9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="8">
-        <f>IF(AND(ISNUMBER(D9),OR(D9&gt;Rubric!$B$7,D9&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A9,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A9,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A9,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IF(C9="N","absent",IF(OR(NOT(ISNUMBER(D9)),NOT(ISNUMBER(F9))),"incomplete",D9+F9))</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(AND(ISNUMBER(D9),OR(D9&gt;Rubric!$B$7,D9&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D9),E9="still failed: presented from the executed notebook",D9&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D9),E9="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A10,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F10" s="8">
-        <f>IF(C10="N","absent",IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(E10))),"incomplete",D10+E10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="8">
-        <f>IF(AND(ISNUMBER(D10),OR(D10&gt;Rubric!$B$7,D10&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A10,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A10,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A10,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>IF(C10="N","absent",IF(OR(NOT(ISNUMBER(D10)),NOT(ISNUMBER(F10))),"incomplete",D10+F10))</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>IF(AND(ISNUMBER(D10),OR(D10&gt;Rubric!$B$7,D10&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D10),E10="still failed: presented from the executed notebook",D10&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D10),E10="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A11,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="8">
-        <f>IF(C11="N","absent",IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(E11))),"incomplete",D11+E11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="8">
-        <f>IF(AND(ISNUMBER(D11),OR(D11&gt;Rubric!$B$7,D11&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A11,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A11,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A11,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>IF(C11="N","absent",IF(OR(NOT(ISNUMBER(D11)),NOT(ISNUMBER(F11))),"incomplete",D11+F11))</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>IF(AND(ISNUMBER(D11),OR(D11&gt;Rubric!$B$7,D11&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D11),E11="still failed: presented from the executed notebook",D11&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D11),E11="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A12,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F12" s="8">
-        <f>IF(C12="N","absent",IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(E12))),"incomplete",D12+E12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>IF(AND(ISNUMBER(D12),OR(D12&gt;Rubric!$B$7,D12&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A12,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A12,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A12,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>IF(C12="N","absent",IF(OR(NOT(ISNUMBER(D12)),NOT(ISNUMBER(F12))),"incomplete",D12+F12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>IF(AND(ISNUMBER(D12),OR(D12&gt;Rubric!$B$7,D12&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D12),E12="still failed: presented from the executed notebook",D12&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D12),E12="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A13,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F13" s="8">
-        <f>IF(C13="N","absent",IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(E13))),"incomplete",D13+E13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="8">
-        <f>IF(AND(ISNUMBER(D13),OR(D13&gt;Rubric!$B$7,D13&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A13,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A13,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A13,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(C13="N","absent",IF(OR(NOT(ISNUMBER(D13)),NOT(ISNUMBER(F13))),"incomplete",D13+F13))</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>IF(AND(ISNUMBER(D13),OR(D13&gt;Rubric!$B$7,D13&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D13),E13="still failed: presented from the executed notebook",D13&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D13),E13="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A14,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F14" s="8">
-        <f>IF(C14="N","absent",IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(E14))),"incomplete",D14+E14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="8">
-        <f>IF(AND(ISNUMBER(D14),OR(D14&gt;Rubric!$B$7,D14&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A14,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A14,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A14,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>IF(C14="N","absent",IF(OR(NOT(ISNUMBER(D14)),NOT(ISNUMBER(F14))),"incomplete",D14+F14))</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>IF(AND(ISNUMBER(D14),OR(D14&gt;Rubric!$B$7,D14&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D14),E14="still failed: presented from the executed notebook",D14&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D14),E14="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A15,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F15" s="8">
-        <f>IF(C15="N","absent",IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(E15))),"incomplete",D15+E15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="8">
-        <f>IF(AND(ISNUMBER(D15),OR(D15&gt;Rubric!$B$7,D15&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A15,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A15,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A15,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="9">
+        <f>IF(C15="N","absent",IF(OR(NOT(ISNUMBER(D15)),NOT(ISNUMBER(F15))),"incomplete",D15+F15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>IF(AND(ISNUMBER(D15),OR(D15&gt;Rubric!$B$7,D15&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D15),E15="still failed: presented from the executed notebook",D15&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D15),E15="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A16,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F16" s="8">
-        <f>IF(C16="N","absent",IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(E16))),"incomplete",D16+E16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="8">
-        <f>IF(AND(ISNUMBER(D16),OR(D16&gt;Rubric!$B$7,D16&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A16,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A16,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A16,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="9">
+        <f>IF(C16="N","absent",IF(OR(NOT(ISNUMBER(D16)),NOT(ISNUMBER(F16))),"incomplete",D16+F16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>IF(AND(ISNUMBER(D16),OR(D16&gt;Rubric!$B$7,D16&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D16),E16="still failed: presented from the executed notebook",D16&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D16),E16="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A17,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F17" s="8">
-        <f>IF(C17="N","absent",IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(E17))),"incomplete",D17+E17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="8">
-        <f>IF(AND(ISNUMBER(D17),OR(D17&gt;Rubric!$B$7,D17&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A17,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A17,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A17,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G17" s="9">
+        <f>IF(C17="N","absent",IF(OR(NOT(ISNUMBER(D17)),NOT(ISNUMBER(F17))),"incomplete",D17+F17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>IF(AND(ISNUMBER(D17),OR(D17&gt;Rubric!$B$7,D17&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D17),E17="still failed: presented from the executed notebook",D17&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D17),E17="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A18,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F18" s="8">
-        <f>IF(C18="N","absent",IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(E18))),"incomplete",D18+E18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="8">
-        <f>IF(AND(ISNUMBER(D18),OR(D18&gt;Rubric!$B$7,D18&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A18,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A18,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A18,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G18" s="9">
+        <f>IF(C18="N","absent",IF(OR(NOT(ISNUMBER(D18)),NOT(ISNUMBER(F18))),"incomplete",D18+F18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>IF(AND(ISNUMBER(D18),OR(D18&gt;Rubric!$B$7,D18&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D18),E18="still failed: presented from the executed notebook",D18&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D18),E18="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A19,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F19" s="8">
-        <f>IF(C19="N","absent",IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(E19))),"incomplete",D19+E19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="8">
-        <f>IF(AND(ISNUMBER(D19),OR(D19&gt;Rubric!$B$7,D19&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A19,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A19,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A19,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G19" s="9">
+        <f>IF(C19="N","absent",IF(OR(NOT(ISNUMBER(D19)),NOT(ISNUMBER(F19))),"incomplete",D19+F19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>IF(AND(ISNUMBER(D19),OR(D19&gt;Rubric!$B$7,D19&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D19),E19="still failed: presented from the executed notebook",D19&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D19),E19="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A20,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>IF(C20="N","absent",IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(E20))),"incomplete",D20+E20))</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>IF(AND(ISNUMBER(D20),OR(D20&gt;Rubric!$B$7,D20&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A20,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A20,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A20,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>IF(C20="N","absent",IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER(F20))),"incomplete",D20+F20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>IF(AND(ISNUMBER(D20),OR(D20&gt;Rubric!$B$7,D20&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D20),E20="still failed: presented from the executed notebook",D20&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D20),E20="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A21,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F21" s="8">
-        <f>IF(C21="N","absent",IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(E21))),"incomplete",D21+E21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="8">
-        <f>IF(AND(ISNUMBER(D21),OR(D21&gt;Rubric!$B$7,D21&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A21,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A21,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A21,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G21" s="9">
+        <f>IF(C21="N","absent",IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER(F21))),"incomplete",D21+F21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>IF(AND(ISNUMBER(D21),OR(D21&gt;Rubric!$B$7,D21&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D21),E21="still failed: presented from the executed notebook",D21&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D21),E21="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A22,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F22" s="8">
-        <f>IF(C22="N","absent",IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(E22))),"incomplete",D22+E22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="8">
-        <f>IF(AND(ISNUMBER(D22),OR(D22&gt;Rubric!$B$7,D22&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A22,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A22,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A22,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G22" s="9">
+        <f>IF(C22="N","absent",IF(OR(NOT(ISNUMBER(D22)),NOT(ISNUMBER(F22))),"incomplete",D22+F22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>IF(AND(ISNUMBER(D22),OR(D22&gt;Rubric!$B$7,D22&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D22),E22="still failed: presented from the executed notebook",D22&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D22),E22="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A23,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F23" s="8">
-        <f>IF(C23="N","absent",IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(E23))),"incomplete",D23+E23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="8">
-        <f>IF(AND(ISNUMBER(D23),OR(D23&gt;Rubric!$B$7,D23&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A23,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A23,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A23,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(C23="N","absent",IF(OR(NOT(ISNUMBER(D23)),NOT(ISNUMBER(F23))),"incomplete",D23+F23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF(AND(ISNUMBER(D23),OR(D23&gt;Rubric!$B$7,D23&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D23),E23="still failed: presented from the executed notebook",D23&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D23),E23="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A24,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F24" s="8">
-        <f>IF(C24="N","absent",IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(E24))),"incomplete",D24+E24))</f>
-        <v/>
-      </c>
-      <c r="G24" s="8">
-        <f>IF(AND(ISNUMBER(D24),OR(D24&gt;Rubric!$B$7,D24&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A24,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A24,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A24,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G24" s="9">
+        <f>IF(C24="N","absent",IF(OR(NOT(ISNUMBER(D24)),NOT(ISNUMBER(F24))),"incomplete",D24+F24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>IF(AND(ISNUMBER(D24),OR(D24&gt;Rubric!$B$7,D24&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D24),E24="still failed: presented from the executed notebook",D24&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D24),E24="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A25,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F25" s="8">
-        <f>IF(C25="N","absent",IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(E25))),"incomplete",D25+E25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="8">
-        <f>IF(AND(ISNUMBER(D25),OR(D25&gt;Rubric!$B$7,D25&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A25,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A25,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A25,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>IF(C25="N","absent",IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(F25))),"incomplete",D25+F25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>IF(AND(ISNUMBER(D25),OR(D25&gt;Rubric!$B$7,D25&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D25),E25="still failed: presented from the executed notebook",D25&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D25),E25="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A26,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F26" s="8">
-        <f>IF(C26="N","absent",IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(E26))),"incomplete",D26+E26))</f>
-        <v/>
-      </c>
-      <c r="G26" s="8">
-        <f>IF(AND(ISNUMBER(D26),OR(D26&gt;Rubric!$B$7,D26&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A26,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A26,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A26,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>IF(C26="N","absent",IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(F26))),"incomplete",D26+F26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>IF(AND(ISNUMBER(D26),OR(D26&gt;Rubric!$B$7,D26&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D26),E26="still failed: presented from the executed notebook",D26&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D26),E26="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A27,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F27" s="8">
-        <f>IF(C27="N","absent",IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(E27))),"incomplete",D27+E27))</f>
-        <v/>
-      </c>
-      <c r="G27" s="8">
-        <f>IF(AND(ISNUMBER(D27),OR(D27&gt;Rubric!$B$7,D27&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A27,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A27,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A27,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>IF(C27="N","absent",IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(F27))),"incomplete",D27+F27))</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF(AND(ISNUMBER(D27),OR(D27&gt;Rubric!$B$7,D27&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D27),E27="still failed: presented from the executed notebook",D27&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D27),E27="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A28,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F28" s="8">
-        <f>IF(C28="N","absent",IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(E28))),"incomplete",D28+E28))</f>
-        <v/>
-      </c>
-      <c r="G28" s="8">
-        <f>IF(AND(ISNUMBER(D28),OR(D28&gt;Rubric!$B$7,D28&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A28,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A28,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A28,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G28" s="9">
+        <f>IF(C28="N","absent",IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(F28))),"incomplete",D28+F28))</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>IF(AND(ISNUMBER(D28),OR(D28&gt;Rubric!$B$7,D28&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D28),E28="still failed: presented from the executed notebook",D28&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D28),E28="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A29,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F29" s="8">
-        <f>IF(C29="N","absent",IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(E29))),"incomplete",D29+E29))</f>
-        <v/>
-      </c>
-      <c r="G29" s="8">
-        <f>IF(AND(ISNUMBER(D29),OR(D29&gt;Rubric!$B$7,D29&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A29,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A29,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A29,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G29" s="9">
+        <f>IF(C29="N","absent",IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(F29))),"incomplete",D29+F29))</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>IF(AND(ISNUMBER(D29),OR(D29&gt;Rubric!$B$7,D29&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D29),E29="still failed: presented from the executed notebook",D29&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D29),E29="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>G7</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A30,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F30" s="8">
-        <f>IF(C30="N","absent",IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(E30))),"incomplete",D30+E30))</f>
-        <v/>
-      </c>
-      <c r="G30" s="8">
-        <f>IF(AND(ISNUMBER(D30),OR(D30&gt;Rubric!$B$7,D30&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A30,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A30,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F30" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A30,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G30" s="9">
+        <f>IF(C30="N","absent",IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(F30))),"incomplete",D30+F30))</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>IF(AND(ISNUMBER(D30),OR(D30&gt;Rubric!$B$7,D30&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D30),E30="still failed: presented from the executed notebook",D30&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D30),E30="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A31,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F31" s="8">
-        <f>IF(C31="N","absent",IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(E31))),"incomplete",D31+E31))</f>
-        <v/>
-      </c>
-      <c r="G31" s="8">
-        <f>IF(AND(ISNUMBER(D31),OR(D31&gt;Rubric!$B$7,D31&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A31,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A31,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F31" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A31,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G31" s="9">
+        <f>IF(C31="N","absent",IF(OR(NOT(ISNUMBER(D31)),NOT(ISNUMBER(F31))),"incomplete",D31+F31))</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF(AND(ISNUMBER(D31),OR(D31&gt;Rubric!$B$7,D31&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D31),E31="still failed: presented from the executed notebook",D31&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D31),E31="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A32,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>IF(C32="N","absent",IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(E32))),"incomplete",D32+E32))</f>
-        <v/>
-      </c>
-      <c r="G32" s="8">
-        <f>IF(AND(ISNUMBER(D32),OR(D32&gt;Rubric!$B$7,D32&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A32,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A32,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F32" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A32,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G32" s="9">
+        <f>IF(C32="N","absent",IF(OR(NOT(ISNUMBER(D32)),NOT(ISNUMBER(F32))),"incomplete",D32+F32))</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>IF(AND(ISNUMBER(D32),OR(D32&gt;Rubric!$B$7,D32&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D32),E32="still failed: presented from the executed notebook",D32&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D32),E32="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A33,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F33" s="8">
-        <f>IF(C33="N","absent",IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(E33))),"incomplete",D33+E33))</f>
-        <v/>
-      </c>
-      <c r="G33" s="8">
-        <f>IF(AND(ISNUMBER(D33),OR(D33&gt;Rubric!$B$7,D33&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A33,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A33,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F33" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A33,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G33" s="9">
+        <f>IF(C33="N","absent",IF(OR(NOT(ISNUMBER(D33)),NOT(ISNUMBER(F33))),"incomplete",D33+F33))</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>IF(AND(ISNUMBER(D33),OR(D33&gt;Rubric!$B$7,D33&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D33),E33="still failed: presented from the executed notebook",D33&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D33),E33="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>G8</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A34,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F34" s="8">
-        <f>IF(C34="N","absent",IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(E34))),"incomplete",D34+E34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="8">
-        <f>IF(AND(ISNUMBER(D34),OR(D34&gt;Rubric!$B$7,D34&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A34,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A34,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F34" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A34,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G34" s="9">
+        <f>IF(C34="N","absent",IF(OR(NOT(ISNUMBER(D34)),NOT(ISNUMBER(F34))),"incomplete",D34+F34))</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>IF(AND(ISNUMBER(D34),OR(D34&gt;Rubric!$B$7,D34&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D34),E34="still failed: presented from the executed notebook",D34&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D34),E34="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A35,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F35" s="8">
-        <f>IF(C35="N","absent",IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(E35))),"incomplete",D35+E35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="8">
-        <f>IF(AND(ISNUMBER(D35),OR(D35&gt;Rubric!$B$7,D35&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A35,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A35,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F35" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A35,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G35" s="9">
+        <f>IF(C35="N","absent",IF(OR(NOT(ISNUMBER(D35)),NOT(ISNUMBER(F35))),"incomplete",D35+F35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>IF(AND(ISNUMBER(D35),OR(D35&gt;Rubric!$B$7,D35&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D35),E35="still failed: presented from the executed notebook",D35&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D35),E35="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A36,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F36" s="8">
-        <f>IF(C36="N","absent",IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(E36))),"incomplete",D36+E36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="8">
-        <f>IF(AND(ISNUMBER(D36),OR(D36&gt;Rubric!$B$7,D36&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A36,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A36,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F36" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A36,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G36" s="9">
+        <f>IF(C36="N","absent",IF(OR(NOT(ISNUMBER(D36)),NOT(ISNUMBER(F36))),"incomplete",D36+F36))</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>IF(AND(ISNUMBER(D36),OR(D36&gt;Rubric!$B$7,D36&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D36),E36="still failed: presented from the executed notebook",D36&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D36),E36="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>G9</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="8">
-        <f>INDEX(Groups!$I$3:$I$11,MATCH(A37,Groups!$A$3:$A$11,0))</f>
-        <v/>
-      </c>
-      <c r="F37" s="8">
-        <f>IF(C37="N","absent",IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(E37))),"incomplete",D37+E37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="8">
-        <f>IF(AND(ISNUMBER(D37),OR(D37&gt;Rubric!$B$7,D37&lt;0)),"above a maximum or below zero","ok")</f>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="9">
+        <f>IF(INDEX(Groups!$E$3:$E$11,MATCH(A37,Groups!$A$3:$A$11,0))="","",INDEX(Groups!$E$3:$E$11,MATCH(A37,Groups!$A$3:$A$11,0)))</f>
+        <v/>
+      </c>
+      <c r="F37" s="9">
+        <f>INDEX(Groups!$J$3:$J$11,MATCH(A37,Groups!$A$3:$A$11,0))</f>
+        <v/>
+      </c>
+      <c r="G37" s="9">
+        <f>IF(C37="N","absent",IF(OR(NOT(ISNUMBER(D37)),NOT(ISNUMBER(F37))),"incomplete",D37+F37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="9">
+        <f>IF(AND(ISNUMBER(D37),OR(D37&gt;Rubric!$B$7,D37&lt;0)),"above a maximum or below zero",IF(AND(ISNUMBER(D37),E37="still failed: presented from the executed notebook",D37&gt;=Rubric!$B$7),"full marks need a demo that ran cold",IF(AND(ISNUMBER(D37),E37="machine failed: demo waits for the reserve"),"score after the demo runs in the reserve","ok")))</f>
         <v/>
       </c>
     </row>
@@ -2106,106 +2357,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Summary</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Summary: is every learner in use scored, inside the rubric and inside the demo rule?</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Seats in use</t>
         </is>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <f>COUNTIF(Learners!C3:C37,"Y")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Learners fully scored</t>
         </is>
       </c>
-      <c r="B4" s="6">
-        <f>COUNT(Learners!F3:F37)</f>
+      <c r="B4" s="7">
+        <f>COUNT(Learners!G3:G37)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Groups with all four group criteria scored</t>
         </is>
       </c>
-      <c r="B5" s="6">
-        <f>COUNT(Groups!I3:I11)</f>
+      <c r="B5" s="7">
+        <f>COUNT(Groups!J3:J11)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Scores above a criterion's maximum or below zero</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <f>COUNTIF(Groups!J3:J11,"above*")+COUNTIF(Learners!G3:G37,"above*")</f>
+      <c r="B6" s="7">
+        <f>COUNTIF(Groups!K3:K11,"above*")+COUNTIF(Learners!H3:H37,"above*")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Rubric total checks</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>IF(Rubric!$B$8=40,"the rubric adds to 40","the rubric adds to "&amp;Rubric!$B$8&amp;", not 40")</f>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Presentation and defence scores that break the demo rule</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>COUNTIF(Learners!H3:H37,"full marks*")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Group part checks</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>IF(Rubric!$B$9=34,"the group part adds to 34","the group part adds to "&amp;Rubric!$B$9&amp;", not 34")</f>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Presentation and defence scores waiting for a demo in the reserve</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>COUNTIF(Learners!H3:H37,"score after*")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>Groups scored with no demo outcome recorded</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>COUNTIF(Groups!K3:K11,"record*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Rubric total check</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>IF(Rubric!$B$8=40,"the rubric adds to 40","the rubric adds to "&amp;Rubric!$B$8&amp;", not 40")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Group part check</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(Rubric!$B$9=34,"the group part adds to 34","the group part adds to "&amp;Rubric!$B$9&amp;", not 34")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B9" s="12">
-        <f>IF(B6&gt;0,B6&amp;" score(s) outside the rubric",IF(B4=B3,"every learner in use is scored",B3-B4&amp;" learners still to score"))</f>
+      <c r="B12" s="13">
+        <f>IF(B6&gt;0,B6&amp;" score(s) outside the rubric",IF(B7&gt;0,B7&amp;" score(s) break the demo rule",IF(B8&gt;0,B8&amp;" score(s) wait for a demo in the reserve",IF(B9&gt;0,B9&amp;" group(s) need the demo's outcome",IF(B4=B3,"every learner in use is scored",B3-B4&amp;" learners still to score")))))</f>
         <v/>
       </c>
     </row>

--- a/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
+++ b/content/W03/SAT/rubrics/C2_W03_SAT_mini_project_scoring_TRAINER.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Build 1's mini project rubric as the requester approved it on 29 September 2026, copied from data/programme/facts.yaml (evaluation.rubrics.W03) onto the Rubric sheet. The first four criteria are scored once for the group, and every member receives those 34 marks; presentation and defence is scored for each learner on 6 marks, so a silent teammate cannot ride the group's score.</t>
+          <t>Build 1's mini project rubric as approved on 29 September 2026, copied from data/programme/facts.yaml (evaluation.rubrics.W03) onto the Rubric sheet. The first four criteria are scored once for the group, and every member receives those 34 marks; presentation and defence is scored for each learner on 6 marks, so a silent teammate cannot ride the group's score.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>After the slot, never in front of the group, from the panel's evidence notes and the question bank (trainer/C2_W03_SAT_question_bank_TRAINER.md). A quiet member's presentation and defence score waits for the separate questions in the room's reserve; the group's 34 does not wait.</t>
+          <t>After the slot, never in front of the group, from the chair's notes of what each member said and the question bank (trainer/C2_W03_SAT_question_bank_TRAINER.md). A quiet member's presentation and defence score waits for the separate questions in the room's reserve; the group's 34 does not wait.</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
         <v/>
       </c>
       <c r="L3" s="6">
-        <f>IF(E3="","record the demo's outcome",IF(E3="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E3="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E3="","record the demo's outcome",IF(E3="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E3="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E3="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -941,7 +941,7 @@
         <v/>
       </c>
       <c r="L4" s="6">
-        <f>IF(E4="","record the demo's outcome",IF(E4="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E4="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E4="","record the demo's outcome",IF(E4="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E4="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E4="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>IF(E5="","record the demo's outcome",IF(E5="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E5="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E5="","record the demo's outcome",IF(E5="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E5="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E5="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -995,7 +995,7 @@
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>IF(E6="","record the demo's outcome",IF(E6="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E6="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E6="","record the demo's outcome",IF(E6="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E6="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E6="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>IF(E7="","record the demo's outcome",IF(E7="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E7="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E7="","record the demo's outcome",IF(E7="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E7="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E7="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="L8" s="6">
-        <f>IF(E8="","record the demo's outcome",IF(E8="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E8="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E8="","record the demo's outcome",IF(E8="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E8="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E8="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="L9" s="6">
-        <f>IF(E9="","record the demo's outcome",IF(E9="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E9="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E9="","record the demo's outcome",IF(E9="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E9="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E9="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="L10" s="6">
-        <f>IF(E10="","record the demo's outcome",IF(E10="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E10="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E10="","record the demo's outcome",IF(E10="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E10="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E10="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>IF(E11="","record the demo's outcome",IF(E11="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E11="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome","the live demo counts as run cold")))</f>
+        <f>IF(E11="","record the demo's outcome",IF(E11="still failed: presented from the executed notebook","the 34 stand on the executed run; presentation and defence scores the demo as not run cold",IF(E11="machine failed: demo waits for the reserve","run the demo cold in the reserve, then record its outcome",IF(E11="recovered within two minutes","the rule sets nothing for a recovery: the panel judges it within presentation and defence","the live demo ran cold"))))</f>
         <v/>
       </c>
     </row>
